--- a/data/trans_camb/P19C02-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P19C02-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 4,55</t>
+          <t>-8,46; 4,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 15,49</t>
+          <t>0,72; 15,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,2; 29,39</t>
+          <t>10,05; 30,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 4,36</t>
+          <t>-8,9; 3,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 10,82</t>
+          <t>-1,65; 11,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 18,29</t>
+          <t>1,63; 19,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 2,47</t>
+          <t>-6,76; 2,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 11,41</t>
+          <t>1,32; 10,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,8; 21,54</t>
+          <t>7,82; 21,77</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-30,86; 20,1</t>
+          <t>-29,48; 20,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,79; 70,93</t>
+          <t>2,54; 69,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,67; 130,98</t>
+          <t>37,0; 134,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,48; 17,28</t>
+          <t>-28,57; 15,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 42,23</t>
+          <t>-5,48; 43,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,9; 70,04</t>
+          <t>5,18; 72,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-23,46; 9,91</t>
+          <t>-23,67; 9,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,47; 45,96</t>
+          <t>4,52; 44,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,74; 84,78</t>
+          <t>26,07; 84,85</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 2,59</t>
+          <t>-8,47; 2,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 7,5</t>
+          <t>-4,49; 7,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,56; 22,92</t>
+          <t>8,69; 24,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 3,95</t>
+          <t>-7,4; 5,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 5,76</t>
+          <t>-6,16; 5,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 18,45</t>
+          <t>-8,54; 18,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 1,85</t>
+          <t>-6,18; 1,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 4,54</t>
+          <t>-3,19; 5,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,01; 18,12</t>
+          <t>0,61; 18,03</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,57; 7,06</t>
+          <t>-20,39; 6,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 20,37</t>
+          <t>-10,7; 20,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,64; 63,87</t>
+          <t>21,56; 66,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,69; 11,46</t>
+          <t>-17,93; 15,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,9; 16,42</t>
+          <t>-14,94; 16,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,78; 50,45</t>
+          <t>-20,91; 51,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 4,91</t>
+          <t>-15,4; 4,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 12,39</t>
+          <t>-7,83; 13,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 48,28</t>
+          <t>1,74; 48,37</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 9,26</t>
+          <t>-2,99; 9,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 11,83</t>
+          <t>1,23; 12,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,8; 26,31</t>
+          <t>13,67; 26,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 10,61</t>
+          <t>-0,36; 10,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,82; 16,09</t>
+          <t>5,05; 16,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,89; 27,75</t>
+          <t>17,54; 28,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 7,98</t>
+          <t>0,23; 8,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,52; 12,87</t>
+          <t>4,26; 12,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,57; 25,85</t>
+          <t>17,33; 25,71</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 27,87</t>
+          <t>-8,34; 27,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,09; 36,39</t>
+          <t>3,28; 39,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35,36; 81,1</t>
+          <t>34,94; 79,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 33,13</t>
+          <t>-1,01; 34,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,67; 51,38</t>
+          <t>13,62; 53,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45,98; 89,23</t>
+          <t>46,49; 90,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 24,74</t>
+          <t>0,53; 25,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,25; 39,42</t>
+          <t>11,28; 39,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>46,86; 79,11</t>
+          <t>46,99; 79,79</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 9,34</t>
+          <t>-3,8; 8,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 12,48</t>
+          <t>-0,08; 12,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 21,38</t>
+          <t>-17,64; 21,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 12,22</t>
+          <t>-0,13; 12,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,14; 17,97</t>
+          <t>5,31; 17,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,98; 25,31</t>
+          <t>9,5; 24,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 9,4</t>
+          <t>0,23; 9,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,4; 13,63</t>
+          <t>4,5; 13,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 21,07</t>
+          <t>-6,65; 21,45</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 34,31</t>
+          <t>-11,17; 31,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 46,04</t>
+          <t>-0,92; 46,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-51,24; 72,31</t>
+          <t>-50,55; 72,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 41,1</t>
+          <t>-0,21; 44,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,11; 62,23</t>
+          <t>15,17; 63,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,94; 88,13</t>
+          <t>29,49; 86,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 32,07</t>
+          <t>0,53; 34,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>12,41; 46,8</t>
+          <t>12,83; 48,14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-17,99; 68,99</t>
+          <t>-20,11; 71,0</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 10,75</t>
+          <t>-2,85; 10,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,41; 15,38</t>
+          <t>1,73; 15,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19,18; 32,46</t>
+          <t>20,32; 32,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 10,79</t>
+          <t>-2,55; 10,59</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,81; 17,07</t>
+          <t>2,89; 16,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,78; 31,48</t>
+          <t>19,75; 31,13</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 8,74</t>
+          <t>-0,65; 9,04</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,98; 14,29</t>
+          <t>4,02; 14,06</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>21,49; 29,68</t>
+          <t>21,72; 30,37</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 67,56</t>
+          <t>-12,38; 64,35</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6,77; 99,38</t>
+          <t>7,36; 96,04</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>82,87; 213,85</t>
+          <t>88,17; 207,79</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 49,67</t>
+          <t>-9,2; 50,09</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>9,88; 77,43</t>
+          <t>9,91; 77,64</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,55; 146,27</t>
+          <t>66,39; 147,54</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 44,71</t>
+          <t>-2,57; 45,58</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>14,55; 71,69</t>
+          <t>15,46; 69,93</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>84,72; 149,89</t>
+          <t>85,12; 158,24</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 9,55</t>
+          <t>-1,94; 9,83</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4,95; 18,47</t>
+          <t>5,96; 19,37</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23,21; 34,92</t>
+          <t>23,69; 35,23</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 7,48</t>
+          <t>-6,5; 7,18</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,83; 20,48</t>
+          <t>5,16; 19,74</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,62; 71,85</t>
+          <t>23,98; 70,76</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 6,34</t>
+          <t>-2,56; 6,39</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>6,62; 17,09</t>
+          <t>7,5; 17,38</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>25,77; 63,11</t>
+          <t>26,14; 64,07</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-23,35; 138,93</t>
+          <t>-15,81; 139,46</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>34,31; 259,31</t>
+          <t>46,54; 285,81</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>169,02; 521,44</t>
+          <t>177,61; 554,15</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-28,07; 53,82</t>
+          <t>-30,4; 51,04</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>27,16; 148,66</t>
+          <t>24,84; 140,56</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>133,64; 573,23</t>
+          <t>128,76; 637,85</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-17,33; 54,23</t>
+          <t>-16,73; 54,63</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>38,01; 142,42</t>
+          <t>44,3; 147,41</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>166,55; 535,85</t>
+          <t>173,1; 596,86</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,98; 16,59</t>
+          <t>3,61; 16,36</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>7,64; 21,22</t>
+          <t>7,41; 21,24</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14,32; 25,95</t>
+          <t>15,2; 26,29</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,94; 11,56</t>
+          <t>1,78; 11,9</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>7,57; 21,1</t>
+          <t>8,06; 22,25</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,97; 27,85</t>
+          <t>18,55; 27,68</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,84; 12,03</t>
+          <t>3,7; 11,53</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>9,98; 19,84</t>
+          <t>9,72; 19,76</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>18,8; 25,75</t>
+          <t>18,7; 26,1</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>17,8; 724,88</t>
+          <t>29,56; 737,45</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>77,71; 986,61</t>
+          <t>75,5; 959,01</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>135,93; 1193,35</t>
+          <t>145,42; 1210,6</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>21,59; 397,8</t>
+          <t>21,01; 477,01</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>84,43; 761,28</t>
+          <t>103,6; 861,85</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>213,71; 1186,57</t>
+          <t>203,49; 991,81</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>48,74; 370,09</t>
+          <t>47,63; 337,36</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>137,3; 617,2</t>
+          <t>132,36; 624,96</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>247,56; 848,74</t>
+          <t>235,59; 887,16</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 3,66</t>
+          <t>-1,25; 3,78</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3,48; 8,79</t>
+          <t>3,42; 8,65</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>5,72; 19,28</t>
+          <t>5,34; 19,18</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 4,61</t>
+          <t>-0,6; 4,48</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>5,48; 10,66</t>
+          <t>5,33; 10,55</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>16,34; 30,13</t>
+          <t>16,6; 29,82</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 3,22</t>
+          <t>-0,24; 3,34</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>5,2; 8,92</t>
+          <t>5,53; 9,17</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>12,9; 22,36</t>
+          <t>12,78; 22,28</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 13,47</t>
+          <t>-4,28; 13,91</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>11,52; 32,0</t>
+          <t>11,37; 31,2</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>20,64; 69,24</t>
+          <t>19,64; 68,68</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 16,85</t>
+          <t>-2,01; 16,04</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>18,18; 38,44</t>
+          <t>17,51; 38,09</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>54,66; 105,87</t>
+          <t>55,69; 103,71</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 11,66</t>
+          <t>-0,71; 12,05</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>17,38; 31,98</t>
+          <t>18,32; 32,88</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>44,04; 79,34</t>
+          <t>43,93; 79,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C02-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P19C02-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19,31</t>
+          <t>19,37</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,76</t>
+          <t>13,34</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14,86</t>
+          <t>16,39</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 4,56</t>
+          <t>-8,62; 4,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 15,38</t>
+          <t>1,23; 14,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,05; 30,13</t>
+          <t>9,92; 28,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 3,78</t>
+          <t>-9,15; 3,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 11,22</t>
+          <t>-1,73; 11,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 19,03</t>
+          <t>5,58; 22,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 2,39</t>
+          <t>-7,1; 2,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 10,92</t>
+          <t>1,24; 10,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,82; 21,77</t>
+          <t>10,19; 22,8</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>60,26%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-29,48; 20,33</t>
+          <t>-29,86; 17,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,54; 69,65</t>
+          <t>4,17; 67,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,0; 134,22</t>
+          <t>34,19; 130,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-28,57; 15,73</t>
+          <t>-28,68; 14,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 43,77</t>
+          <t>-5,52; 45,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,18; 72,13</t>
+          <t>17,65; 88,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-23,67; 9,39</t>
+          <t>-23,81; 8,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,52; 44,21</t>
+          <t>4,43; 43,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,07; 84,85</t>
+          <t>35,09; 90,76</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16,28</t>
+          <t>16,98</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,43</t>
+          <t>15,8</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11,87</t>
+          <t>16,33</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 2,29</t>
+          <t>-8,88; 3,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 7,47</t>
+          <t>-4,96; 7,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,69; 24,17</t>
+          <t>9,43; 23,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 5,13</t>
+          <t>-8,29; 3,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 5,91</t>
+          <t>-6,08; 5,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 18,7</t>
+          <t>9,4; 22,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 1,65</t>
+          <t>-7,17; 1,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 5,05</t>
+          <t>-3,25; 4,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 18,03</t>
+          <t>11,68; 20,77</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>42,32%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,39; 6,4</t>
+          <t>-21,16; 8,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 20,76</t>
+          <t>-11,74; 19,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,56; 66,43</t>
+          <t>22,8; 66,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,93; 15,14</t>
+          <t>-19,87; 11,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 16,6</t>
+          <t>-14,94; 16,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,91; 51,61</t>
+          <t>22,82; 63,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,4; 4,61</t>
+          <t>-17,3; 4,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 13,8</t>
+          <t>-8,05; 13,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 48,37</t>
+          <t>28,64; 56,48</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20,31</t>
+          <t>18,81</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,84</t>
+          <t>22,1</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21,66</t>
+          <t>20,54</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 9,12</t>
+          <t>-3,92; 8,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 12,8</t>
+          <t>-0,44; 12,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,67; 26,15</t>
+          <t>12,13; 24,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 10,7</t>
+          <t>-0,12; 10,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,05; 16,53</t>
+          <t>4,55; 15,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,54; 28,05</t>
+          <t>16,54; 26,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 8,36</t>
+          <t>0,45; 8,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,26; 12,88</t>
+          <t>4,37; 12,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,33; 25,71</t>
+          <t>16,48; 24,58</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>58,85%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 27,58</t>
+          <t>-10,08; 26,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,28; 39,43</t>
+          <t>-0,51; 38,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34,94; 79,18</t>
+          <t>30,88; 76,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 34,01</t>
+          <t>-0,47; 34,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,62; 53,26</t>
+          <t>12,11; 50,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>46,49; 90,6</t>
+          <t>44,48; 86,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,53; 25,39</t>
+          <t>1,19; 25,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,28; 39,6</t>
+          <t>11,62; 38,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>46,99; 79,79</t>
+          <t>44,21; 74,53</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>19,11</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,44</t>
+          <t>22,08</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11,38</t>
+          <t>20,64</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 8,82</t>
+          <t>-2,7; 9,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 12,79</t>
+          <t>0,42; 12,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,64; 21,34</t>
+          <t>12,9; 25,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 12,58</t>
+          <t>0,15; 12,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,31; 17,86</t>
+          <t>5,73; 17,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,5; 24,82</t>
+          <t>16,74; 27,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 9,71</t>
+          <t>0,51; 9,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,5; 13,87</t>
+          <t>4,57; 13,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 21,45</t>
+          <t>16,47; 24,66</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>65,27%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 31,56</t>
+          <t>-8,05; 33,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 46,25</t>
+          <t>1,63; 47,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-50,55; 72,21</t>
+          <t>37,46; 92,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 44,17</t>
+          <t>0,45; 43,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,17; 63,13</t>
+          <t>16,15; 62,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,49; 86,29</t>
+          <t>46,46; 98,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,53; 34,35</t>
+          <t>1,53; 33,4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>12,83; 48,14</t>
+          <t>13,14; 46,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 71,0</t>
+          <t>48,61; 85,54</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26,28</t>
+          <t>26,79</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,28</t>
+          <t>26,39</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>26,02</t>
+          <t>26,37</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 10,3</t>
+          <t>-2,45; 10,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,73; 15,4</t>
+          <t>2,04; 15,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20,32; 32,28</t>
+          <t>20,34; 32,65</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 10,59</t>
+          <t>-2,92; 10,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,89; 16,23</t>
+          <t>3,51; 17,3</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,75; 31,13</t>
+          <t>19,75; 31,78</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 9,04</t>
+          <t>-0,56; 8,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,02; 14,06</t>
+          <t>4,72; 14,01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>21,72; 30,37</t>
+          <t>22,0; 30,5</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>135,57%</t>
+          <t>138,2%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>104,95%</t>
+          <t>105,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>116,0%</t>
+          <t>117,55%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 64,35</t>
+          <t>-10,47; 66,36</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7,36; 96,04</t>
+          <t>8,23; 102,91</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>88,17; 207,79</t>
+          <t>86,22; 212,99</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 50,09</t>
+          <t>-10,43; 51,67</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>9,91; 77,64</t>
+          <t>11,63; 78,53</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,39; 147,54</t>
+          <t>66,91; 156,31</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 45,58</t>
+          <t>-2,29; 41,83</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>15,46; 69,93</t>
+          <t>19,04; 69,18</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>85,12; 158,24</t>
+          <t>85,28; 155,35</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29,41</t>
+          <t>30,63</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>45,24</t>
+          <t>26,31</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>39,98</t>
+          <t>28,26</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 9,83</t>
+          <t>-2,3; 10,01</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>5,96; 19,37</t>
+          <t>5,12; 18,56</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23,69; 35,23</t>
+          <t>24,52; 36,55</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 7,18</t>
+          <t>-5,87; 7,58</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,16; 19,74</t>
+          <t>4,66; 20,21</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,98; 70,76</t>
+          <t>19,72; 32,16</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 6,39</t>
+          <t>-2,21; 6,79</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>7,5; 17,38</t>
+          <t>7,34; 17,03</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>26,14; 64,07</t>
+          <t>24,11; 32,23</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>297,65%</t>
+          <t>310,01%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>258,84%</t>
+          <t>150,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>286,55%</t>
+          <t>202,5%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-15,81; 139,46</t>
+          <t>-17,68; 140,74</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>46,54; 285,81</t>
+          <t>39,37; 260,05</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>177,61; 554,15</t>
+          <t>174,37; 548,11</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-30,4; 51,04</t>
+          <t>-27,91; 52,14</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>24,84; 140,56</t>
+          <t>21,69; 141,77</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>128,76; 637,85</t>
+          <t>85,14; 237,18</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 54,63</t>
+          <t>-14,62; 57,22</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>44,3; 147,41</t>
+          <t>45,26; 146,51</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>173,1; 596,86</t>
+          <t>141,14; 292,45</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20,85</t>
+          <t>21,33</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,68</t>
+          <t>24,42</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>22,53</t>
+          <t>23,16</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>3,61; 16,36</t>
+          <t>3,22; 16,4</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>7,41; 21,24</t>
+          <t>7,62; 21,39</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15,2; 26,29</t>
+          <t>15,31; 26,73</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,78; 11,9</t>
+          <t>2,09; 11,82</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,06; 22,25</t>
+          <t>8,4; 21,31</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,55; 27,68</t>
+          <t>19,45; 28,95</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,7; 11,53</t>
+          <t>3,94; 11,62</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>9,72; 19,76</t>
+          <t>9,92; 19,74</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>18,7; 26,1</t>
+          <t>19,63; 26,86</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>431,46%</t>
+          <t>441,39%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>470,07%</t>
+          <t>484,92%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>454,31%</t>
+          <t>467,1%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>29,56; 737,45</t>
+          <t>16,98; 690,51</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>75,5; 959,01</t>
+          <t>71,09; 900,43</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>145,42; 1210,6</t>
+          <t>152,43; 1259,5</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>21,01; 477,01</t>
+          <t>24,78; 452,18</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>103,6; 861,85</t>
+          <t>100,12; 769,81</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>203,49; 991,81</t>
+          <t>219,76; 1182,16</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>47,63; 337,36</t>
+          <t>54,26; 382,32</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>132,36; 624,96</t>
+          <t>140,43; 642,19</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>235,59; 887,16</t>
+          <t>259,94; 899,97</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>14,93</t>
+          <t>18,54</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>20,69</t>
+          <t>19,54</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>17,9</t>
+          <t>19,05</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,78</t>
+          <t>-1,63; 3,79</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3,42; 8,65</t>
+          <t>3,35; 8,8</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>5,34; 19,18</t>
+          <t>15,74; 21,04</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 4,48</t>
+          <t>-0,52; 4,34</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>5,33; 10,55</t>
+          <t>5,44; 10,47</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>16,6; 29,82</t>
+          <t>17,29; 21,79</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 3,34</t>
+          <t>-0,07; 3,45</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>5,53; 9,17</t>
+          <t>5,44; 9,08</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>12,78; 22,28</t>
+          <t>17,19; 20,7</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>65,98%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 13,91</t>
+          <t>-5,43; 14,0</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>11,37; 31,2</t>
+          <t>11,23; 32,68</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>19,64; 68,68</t>
+          <t>51,99; 77,5</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 16,04</t>
+          <t>-1,7; 15,54</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>17,51; 38,09</t>
+          <t>18,08; 37,38</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>55,69; 103,71</t>
+          <t>55,9; 78,71</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 12,05</t>
+          <t>-0,25; 12,28</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>18,32; 32,88</t>
+          <t>18,37; 32,8</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>43,93; 79,59</t>
+          <t>57,68; 74,06</t>
         </is>
       </c>
     </row>
